--- a/Standard Operating Procedures/SOPs Table of Contents.xlsx
+++ b/Standard Operating Procedures/SOPs Table of Contents.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="14.75" customWidth="1" style="16" min="2" max="2"/>
@@ -665,42 +665,45 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tr4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mutant Vehicle Statement of Intent (BMorg)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="12" t="n"/>
+      <c r="E14" s="11" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Art Car</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>SirKiss Setup and Operation, parts list</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>AC2</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Sound System</t>
         </is>
       </c>
       <c r="E15" s="11" t="n"/>
@@ -709,45 +712,45 @@
       <c r="A16" s="12" t="n"/>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>AC3</t>
+          <t>AC2</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Generator Spec Sheet, parts list, PM checklist</t>
+          <t>Sound System</t>
         </is>
       </c>
       <c r="E16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n"/>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Facilities</t>
-        </is>
-      </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Fc1</t>
+          <t>AC3</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Plumbing Diagram, parts list</t>
+          <t>Generator Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Fc2</t>
+          <t>Fc1</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Supplies Shopping List</t>
+          <t>Plumbing Diagram, parts list</t>
         </is>
       </c>
       <c r="E18" s="11" t="n"/>
@@ -756,40 +759,40 @@
       <c r="A19" s="12" t="n"/>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Fc3</t>
+          <t>Fc2</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Supplies Shopping List</t>
         </is>
       </c>
       <c r="E19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>PM1</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Isuzu Spec Sheet, parts list, PM checklist</t>
+          <t>Fc3</t>
         </is>
       </c>
       <c r="E20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n"/>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>PM2</t>
+          <t>PM1</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Refrigeration Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Isuzu Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E21" s="11" t="n"/>
@@ -798,12 +801,12 @@
       <c r="A22" s="12" t="n"/>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>PM3</t>
+          <t>PM2</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Cargo Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Refrigeration Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E22" s="11" t="n"/>
@@ -812,12 +815,12 @@
       <c r="A23" s="12" t="n"/>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>PM4</t>
+          <t>PM3</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Porta Potties Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Cargo Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E23" s="11" t="n"/>
@@ -826,45 +829,45 @@
       <c r="A24" s="12" t="n"/>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>PM5</t>
+          <t>PM4</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Generator Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Porta Potties Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n"/>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Power Grid</t>
-        </is>
-      </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Pow1</t>
+          <t>PM5</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Grid Scamatics</t>
+          <t>Generator Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Pow2</t>
+          <t>Pow1</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Generator Spec Sheet, parts list, PM checklist</t>
+          <t>Grid Scamatics</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -873,45 +876,45 @@
       <c r="A27" s="12" t="n"/>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Pow3</t>
+          <t>Pow2</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Fuel Containment</t>
+          <t>Generator Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Shelter</t>
-        </is>
-      </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Sh1</t>
+          <t>Pow3</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Shade Structure Setup, parts list</t>
+          <t>Fuel Containment</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n"/>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Shelter</t>
+        </is>
+      </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Sh2</t>
+          <t>Sh1</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Sound System</t>
+          <t>Shade Structure Setup, parts list</t>
         </is>
       </c>
       <c r="E29" s="11" t="n"/>
@@ -920,18 +923,28 @@
       <c r="A30" s="12" t="n"/>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Sh3</t>
+          <t>Sh2</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Fire Poofer</t>
+          <t>Sound System</t>
         </is>
       </c>
       <c r="E30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n"/>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Sh3</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Fire Poofer</t>
+        </is>
+      </c>
       <c r="E31" s="11" t="n"/>
     </row>
     <row r="32">
@@ -939,57 +952,42 @@
       <c r="E32" s="11" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Committees</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Log1</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>Trailer Hitch &amp; GVW Specs</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Log2</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Camp Layout Map</t>
         </is>
       </c>
       <c r="E34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n"/>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Safe1</t>
+          <t>Log2</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Hazards and Training</t>
+          <t>Camp Layout Map</t>
         </is>
       </c>
       <c r="E35" s="11" t="n"/>
@@ -998,31 +996,36 @@
       <c r="A36" s="12" t="n"/>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Kch1</t>
+          <t>Safe1</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Kitchen Layout</t>
+          <t>Hazards and Training</t>
         </is>
       </c>
       <c r="E36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n"/>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Kch2</t>
+          <t>Kch1</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Health Department Compliance</t>
+          <t>Kitchen Layout</t>
         </is>
       </c>
       <c r="E37" s="11" t="n"/>
@@ -1031,45 +1034,45 @@
       <c r="A38" s="12" t="n"/>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Kch3</t>
+          <t>Kch2</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Food Menu and Shopping List</t>
+          <t>Health Department Compliance</t>
         </is>
       </c>
       <c r="E38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n"/>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Bar &amp; Beverage</t>
-        </is>
-      </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Bev1</t>
+          <t>Kch3</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Keg Trailer Systems</t>
+          <t>Food Menu and Shopping List</t>
         </is>
       </c>
       <c r="E39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Bar &amp; Beverage</t>
+        </is>
+      </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Bev2</t>
+          <t>Bev1</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Keg Filling</t>
+          <t>Keg Trailer Systems</t>
         </is>
       </c>
       <c r="E40" s="11" t="n"/>
@@ -1078,31 +1081,26 @@
       <c r="A41" s="12" t="n"/>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Bev3</t>
+          <t>Bev2</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Beverage Menu and Shopping List</t>
+          <t>Keg Filling</t>
         </is>
       </c>
       <c r="E41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Events</t>
-        </is>
-      </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Eve1</t>
+          <t>Bev3</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Signup Monkey</t>
+          <t>Beverage Menu and Shopping List</t>
         </is>
       </c>
       <c r="E42" s="11" t="n"/>
@@ -1111,12 +1109,12 @@
       <c r="A43" s="12" t="n"/>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>LNT1</t>
+          <t>Eve1</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -1128,6 +1126,21 @@
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>LNT</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>LNT1</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Signup Monkey</t>
+        </is>
+      </c>
       <c r="E44" s="11" t="n"/>
     </row>
     <row r="45">
@@ -1163,11 +1176,15 @@
       <c r="E52" s="11" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="n"/>
-      <c r="B53" s="14" t="n"/>
-      <c r="C53" s="14" t="n"/>
-      <c r="D53" s="14" t="n"/>
-      <c r="E53" s="15" t="n"/>
+      <c r="A53" s="12" t="n"/>
+      <c r="E53" s="11" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="14" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="14" t="n"/>
+      <c r="E54" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Standard Operating Procedures/SOPs Table of Contents.xlsx
+++ b/Standard Operating Procedures/SOPs Table of Contents.xlsx
@@ -541,7 +541,11 @@
           <t>Slack</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n"/>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n"/>
@@ -555,7 +559,11 @@
           <t>Sakari</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n"/>
@@ -569,7 +577,11 @@
           <t>HubSpot</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n"/>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n"/>
@@ -665,17 +677,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>Tr4</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>Mutant Vehicle Statement of Intent (BMorg)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>

--- a/Standard Operating Procedures/SOPs Table of Contents.xlsx
+++ b/Standard Operating Procedures/SOPs Table of Contents.xlsx
@@ -653,10 +653,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>501c3 Administration</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n"/>
+          <t>IRS 509(a)(2) Administration</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>

--- a/Standard Operating Procedures/SOPs Table of Contents.xlsx
+++ b/Standard Operating Procedures/SOPs Table of Contents.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="14.75" customWidth="1" style="16" min="2" max="2"/>
@@ -584,34 +584,37 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Human Resources</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>HR1</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Onboarding Questionaire</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="n"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Com4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Role Email Address Setup</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR2</t>
+          <t>HR1</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Camp Integration and FAQs</t>
+          <t>Onboarding Questionaire</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -620,120 +623,120 @@
       <c r="A9" s="12" t="n"/>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR3</t>
+          <t>HR2</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Camp Integration and FAQs</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n"/>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Treasurer</t>
-        </is>
-      </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Tr1</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Accounting and Budgets</t>
+          <t>HR3</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Treasurer</t>
+        </is>
+      </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Tr2</t>
+          <t>Tr1</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>IRS 509(a)(2) Administration</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+          <t>Accounting and Budgets</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>
       <c r="C12" s="10" t="inlineStr">
         <is>
+          <t>Tr2</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>IRS 509(a)(2) Administration</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
           <t>Tr3</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Statement of Intent (BMorg)</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="0" t="inlineStr">
+    <row r="14">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>Tr4</t>
         </is>
       </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>Mutant Vehicle Statement of Intent (BMorg)</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="E14" s="11" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="12" t="n"/>
+      <c r="E15" s="11" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Art Car</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>SirKiss Setup and Operation, parts list</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>AC2</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Sound System</t>
         </is>
       </c>
       <c r="E16" s="11" t="n"/>
@@ -742,45 +745,45 @@
       <c r="A17" s="12" t="n"/>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>AC3</t>
+          <t>AC2</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Generator Spec Sheet, parts list, PM checklist</t>
+          <t>Sound System</t>
         </is>
       </c>
       <c r="E17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Facilities</t>
-        </is>
-      </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Fc1</t>
+          <t>AC3</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Plumbing Diagram, parts list</t>
+          <t>Generator Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n"/>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Fc2</t>
+          <t>Fc1</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Supplies Shopping List</t>
+          <t>Plumbing Diagram, parts list</t>
         </is>
       </c>
       <c r="E19" s="11" t="n"/>
@@ -789,40 +792,40 @@
       <c r="A20" s="12" t="n"/>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Fc3</t>
+          <t>Fc2</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Supplies Shopping List</t>
         </is>
       </c>
       <c r="E20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n"/>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>PM1</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Isuzu Spec Sheet, parts list, PM checklist</t>
+          <t>Fc3</t>
         </is>
       </c>
       <c r="E21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>PM2</t>
+          <t>PM1</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Refrigeration Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Isuzu Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E22" s="11" t="n"/>
@@ -831,12 +834,12 @@
       <c r="A23" s="12" t="n"/>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>PM3</t>
+          <t>PM2</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Cargo Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Refrigeration Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E23" s="11" t="n"/>
@@ -845,12 +848,12 @@
       <c r="A24" s="12" t="n"/>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>PM4</t>
+          <t>PM3</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Porta Potties Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Cargo Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E24" s="11" t="n"/>
@@ -859,45 +862,45 @@
       <c r="A25" s="12" t="n"/>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>PM5</t>
+          <t>PM4</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Generator Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Porta Potties Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Power Grid</t>
-        </is>
-      </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Pow1</t>
+          <t>PM5</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Grid Scamatics</t>
+          <t>Generator Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n"/>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Pow2</t>
+          <t>Pow1</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Generator Spec Sheet, parts list, PM checklist</t>
+          <t>Grid Scamatics</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -906,45 +909,45 @@
       <c r="A28" s="12" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Pow3</t>
+          <t>Pow2</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Fuel Containment</t>
+          <t>Generator Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n"/>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Shelter</t>
-        </is>
-      </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Sh1</t>
+          <t>Pow3</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Shade Structure Setup, parts list</t>
+          <t>Fuel Containment</t>
         </is>
       </c>
       <c r="E29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Shelter</t>
+        </is>
+      </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Sh2</t>
+          <t>Sh1</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Sound System</t>
+          <t>Shade Structure Setup, parts list</t>
         </is>
       </c>
       <c r="E30" s="11" t="n"/>
@@ -953,18 +956,28 @@
       <c r="A31" s="12" t="n"/>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Sh3</t>
+          <t>Sh2</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Fire Poofer</t>
+          <t>Sound System</t>
         </is>
       </c>
       <c r="E31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n"/>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Sh3</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Fire Poofer</t>
+        </is>
+      </c>
       <c r="E32" s="11" t="n"/>
     </row>
     <row r="33">
@@ -972,57 +985,42 @@
       <c r="E33" s="11" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="12" t="n"/>
+      <c r="E34" s="11" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Committees</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Log1</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Trailer Hitch &amp; GVW Specs</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n"/>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Log2</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Camp Layout Map</t>
         </is>
       </c>
       <c r="E35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n"/>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Safe1</t>
+          <t>Log2</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Hazards and Training</t>
+          <t>Camp Layout Map</t>
         </is>
       </c>
       <c r="E36" s="11" t="n"/>
@@ -1031,31 +1029,36 @@
       <c r="A37" s="12" t="n"/>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Kch1</t>
+          <t>Safe1</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Kitchen Layout</t>
+          <t>Hazards and Training</t>
         </is>
       </c>
       <c r="E37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n"/>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Kch2</t>
+          <t>Kch1</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Health Department Compliance</t>
+          <t>Kitchen Layout</t>
         </is>
       </c>
       <c r="E38" s="11" t="n"/>
@@ -1064,45 +1067,45 @@
       <c r="A39" s="12" t="n"/>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Kch3</t>
+          <t>Kch2</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Food Menu and Shopping List</t>
+          <t>Health Department Compliance</t>
         </is>
       </c>
       <c r="E39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Bar &amp; Beverage</t>
-        </is>
-      </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Bev1</t>
+          <t>Kch3</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Keg Trailer Systems</t>
+          <t>Food Menu and Shopping List</t>
         </is>
       </c>
       <c r="E40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n"/>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Bar &amp; Beverage</t>
+        </is>
+      </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Bev2</t>
+          <t>Bev1</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Keg Filling</t>
+          <t>Keg Trailer Systems</t>
         </is>
       </c>
       <c r="E41" s="11" t="n"/>
@@ -1111,31 +1114,26 @@
       <c r="A42" s="12" t="n"/>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Bev3</t>
+          <t>Bev2</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Beverage Menu and Shopping List</t>
+          <t>Keg Filling</t>
         </is>
       </c>
       <c r="E42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="n"/>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Events</t>
-        </is>
-      </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Eve1</t>
+          <t>Bev3</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Signup Monkey</t>
+          <t>Beverage Menu and Shopping List</t>
         </is>
       </c>
       <c r="E43" s="11" t="n"/>
@@ -1144,12 +1142,12 @@
       <c r="A44" s="12" t="n"/>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>LNT1</t>
+          <t>Eve1</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -1161,6 +1159,21 @@
     </row>
     <row r="45">
       <c r="A45" s="12" t="n"/>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>LNT</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>LNT1</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Signup Monkey</t>
+        </is>
+      </c>
       <c r="E45" s="11" t="n"/>
     </row>
     <row r="46">
@@ -1196,11 +1209,15 @@
       <c r="E53" s="11" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="n"/>
-      <c r="B54" s="14" t="n"/>
-      <c r="C54" s="14" t="n"/>
-      <c r="D54" s="14" t="n"/>
-      <c r="E54" s="15" t="n"/>
+      <c r="A54" s="12" t="n"/>
+      <c r="E54" s="11" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="14" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="14" t="n"/>
+      <c r="E55" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Standard Operating Procedures/SOPs Table of Contents.xlsx
+++ b/Standard Operating Procedures/SOPs Table of Contents.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="14.75" customWidth="1" style="16" min="2" max="2"/>
@@ -584,17 +584,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Com4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>Role Email Address Setup</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -715,42 +715,45 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Tr5</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Hell Station Petrol Application (BMorg)</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="12" t="n"/>
+      <c r="E16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Art Car</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>SirKiss Setup and Operation, parts list</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>AC2</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Sound System</t>
         </is>
       </c>
       <c r="E17" s="11" t="n"/>
@@ -759,45 +762,45 @@
       <c r="A18" s="12" t="n"/>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>AC3</t>
+          <t>AC2</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Generator Spec Sheet, parts list, PM checklist</t>
+          <t>Sound System</t>
         </is>
       </c>
       <c r="E18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n"/>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Facilities</t>
-        </is>
-      </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Fc1</t>
+          <t>AC3</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Plumbing Diagram, parts list</t>
+          <t>Generator Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Fc2</t>
+          <t>Fc1</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Supplies Shopping List</t>
+          <t>Plumbing Diagram, parts list</t>
         </is>
       </c>
       <c r="E20" s="11" t="n"/>
@@ -806,40 +809,40 @@
       <c r="A21" s="12" t="n"/>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Fc3</t>
+          <t>Fc2</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Supplies Shopping List</t>
         </is>
       </c>
       <c r="E21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>PM1</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Isuzu Spec Sheet, parts list, PM checklist</t>
+          <t>Fc3</t>
         </is>
       </c>
       <c r="E22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n"/>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>PM2</t>
+          <t>PM1</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Refrigeration Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Isuzu Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E23" s="11" t="n"/>
@@ -848,12 +851,12 @@
       <c r="A24" s="12" t="n"/>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>PM3</t>
+          <t>PM2</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Cargo Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Refrigeration Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E24" s="11" t="n"/>
@@ -862,12 +865,12 @@
       <c r="A25" s="12" t="n"/>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>PM4</t>
+          <t>PM3</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Porta Potties Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Cargo Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E25" s="11" t="n"/>
@@ -876,45 +879,45 @@
       <c r="A26" s="12" t="n"/>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>PM5</t>
+          <t>PM4</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Generator Trailer Spec Sheet, parts list, PM checklist</t>
+          <t>Porta Potties Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n"/>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Power Grid</t>
-        </is>
-      </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Pow1</t>
+          <t>PM5</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Grid Scamatics</t>
+          <t>Generator Trailer Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Pow2</t>
+          <t>Pow1</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Generator Spec Sheet, parts list, PM checklist</t>
+          <t>Grid Scamatics</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>
@@ -923,45 +926,45 @@
       <c r="A29" s="12" t="n"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Pow3</t>
+          <t>Pow2</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Fuel Containment</t>
+          <t>Generator Spec Sheet, parts list, PM checklist</t>
         </is>
       </c>
       <c r="E29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Shelter</t>
-        </is>
-      </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Sh1</t>
+          <t>Pow3</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Shade Structure Setup, parts list</t>
+          <t>Fuel Containment</t>
         </is>
       </c>
       <c r="E30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n"/>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Shelter</t>
+        </is>
+      </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Sh2</t>
+          <t>Sh1</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Sound System</t>
+          <t>Shade Structure Setup, parts list</t>
         </is>
       </c>
       <c r="E31" s="11" t="n"/>
@@ -970,18 +973,28 @@
       <c r="A32" s="12" t="n"/>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Sh3</t>
+          <t>Sh2</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Fire Poofer</t>
+          <t>Sound System</t>
         </is>
       </c>
       <c r="E32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n"/>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Sh3</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Fire Poofer</t>
+        </is>
+      </c>
       <c r="E33" s="11" t="n"/>
     </row>
     <row r="34">
@@ -989,57 +1002,42 @@
       <c r="E34" s="11" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="12" t="n"/>
+      <c r="E35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Committees</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Log1</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Trailer Hitch &amp; GVW Specs</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n"/>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>Log2</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Camp Layout Map</t>
         </is>
       </c>
       <c r="E36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n"/>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Safe1</t>
+          <t>Log2</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Hazards and Training</t>
+          <t>Camp Layout Map</t>
         </is>
       </c>
       <c r="E37" s="11" t="n"/>
@@ -1048,31 +1046,36 @@
       <c r="A38" s="12" t="n"/>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Kch1</t>
+          <t>Safe1</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Kitchen Layout</t>
+          <t>Hazards and Training</t>
         </is>
       </c>
       <c r="E38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n"/>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Kch2</t>
+          <t>Kch1</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Health Department Compliance</t>
+          <t>Kitchen Layout</t>
         </is>
       </c>
       <c r="E39" s="11" t="n"/>
@@ -1081,45 +1084,45 @@
       <c r="A40" s="12" t="n"/>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Kch3</t>
+          <t>Kch2</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Food Menu and Shopping List</t>
+          <t>Health Department Compliance</t>
         </is>
       </c>
       <c r="E40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n"/>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Bar &amp; Beverage</t>
-        </is>
-      </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Bev1</t>
+          <t>Kch3</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Keg Trailer Systems</t>
+          <t>Food Menu and Shopping List</t>
         </is>
       </c>
       <c r="E41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Bar &amp; Beverage</t>
+        </is>
+      </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Bev2</t>
+          <t>Bev1</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Keg Filling</t>
+          <t>Keg Trailer Systems</t>
         </is>
       </c>
       <c r="E42" s="11" t="n"/>
@@ -1128,31 +1131,26 @@
       <c r="A43" s="12" t="n"/>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Bev3</t>
+          <t>Bev2</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Beverage Menu and Shopping List</t>
+          <t>Keg Filling</t>
         </is>
       </c>
       <c r="E43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>Events</t>
-        </is>
-      </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Eve1</t>
+          <t>Bev3</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Signup Monkey</t>
+          <t>Beverage Menu and Shopping List</t>
         </is>
       </c>
       <c r="E44" s="11" t="n"/>
@@ -1161,12 +1159,12 @@
       <c r="A45" s="12" t="n"/>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>LNT1</t>
+          <t>Eve1</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -1178,6 +1176,21 @@
     </row>
     <row r="46">
       <c r="A46" s="12" t="n"/>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>LNT</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>LNT1</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Signup Monkey</t>
+        </is>
+      </c>
       <c r="E46" s="11" t="n"/>
     </row>
     <row r="47">
@@ -1213,11 +1226,15 @@
       <c r="E54" s="11" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="n"/>
-      <c r="B55" s="14" t="n"/>
-      <c r="C55" s="14" t="n"/>
-      <c r="D55" s="14" t="n"/>
-      <c r="E55" s="15" t="n"/>
+      <c r="A55" s="12" t="n"/>
+      <c r="E55" s="11" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="14" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="14" t="n"/>
+      <c r="E56" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
